--- a/AAII_Financials/Yearly/DCX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DCX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>DCX</t>
   </si>
@@ -714,11 +714,11 @@
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>6900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>9500</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G8" s="3">
         <v>15000</v>
@@ -744,11 +744,11 @@
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3">
-        <v>31700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>42200</v>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G9" s="3">
         <v>53300</v>
@@ -774,11 +774,11 @@
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-32800</v>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G10" s="3">
         <v>-38300</v>
@@ -818,11 +818,11 @@
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>8400</v>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G12" s="3">
         <v>13800</v>
@@ -878,11 +878,11 @@
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>500</v>
-      </c>
-      <c r="F14" s="3">
-        <v>800</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>800</v>
@@ -950,10 +950,10 @@
         <v>8400</v>
       </c>
       <c r="E17" s="3">
-        <v>64100</v>
+        <v>2400</v>
       </c>
       <c r="F17" s="3">
-        <v>97900</v>
+        <v>3600</v>
       </c>
       <c r="G17" s="3">
         <v>132400</v>
@@ -980,10 +980,10 @@
         <v>-8400</v>
       </c>
       <c r="E18" s="3">
-        <v>-57200</v>
+        <v>-2400</v>
       </c>
       <c r="F18" s="3">
-        <v>-88400</v>
+        <v>-3600</v>
       </c>
       <c r="G18" s="3">
         <v>-117400</v>
@@ -1023,11 +1023,11 @@
       <c r="D20" s="3">
         <v>-79100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-4900</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
         <v>-20600</v>
@@ -1054,10 +1054,10 @@
         <v>93800</v>
       </c>
       <c r="E21" s="3">
-        <v>-28900</v>
+        <v>20700</v>
       </c>
       <c r="F21" s="3">
-        <v>-48900</v>
+        <v>31000</v>
       </c>
       <c r="G21" s="3">
         <v>-52100</v>
@@ -1083,11 +1083,11 @@
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>16600</v>
-      </c>
-      <c r="F22" s="3">
-        <v>14800</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>14700</v>
@@ -1114,10 +1114,10 @@
         <v>70700</v>
       </c>
       <c r="E23" s="3">
-        <v>-69000</v>
+        <v>-2400</v>
       </c>
       <c r="F23" s="3">
-        <v>-98500</v>
+        <v>-3600</v>
       </c>
       <c r="G23" s="3">
         <v>-111500</v>
@@ -1204,10 +1204,10 @@
         <v>70700</v>
       </c>
       <c r="E26" s="3">
-        <v>-69000</v>
+        <v>-2400</v>
       </c>
       <c r="F26" s="3">
-        <v>-98500</v>
+        <v>-3600</v>
       </c>
       <c r="G26" s="3">
         <v>-111500</v>
@@ -1231,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-9900</v>
+        <v>-3600</v>
       </c>
       <c r="E27" s="3">
         <v>-46900</v>
@@ -1294,10 +1294,10 @@
         <v>-100700</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-66600</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-94900</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1383,11 +1383,11 @@
       <c r="D32" s="3">
         <v>79100</v>
       </c>
-      <c r="E32" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>4900</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
         <v>20600</v>
@@ -1567,7 +1567,7 @@
         <v>3900</v>
       </c>
       <c r="E41" s="3">
-        <v>3700</v>
+        <v>1700</v>
       </c>
       <c r="F41" s="3">
         <v>10700</v>
@@ -1626,8 +1626,8 @@
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
-        <v>40400</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F43" s="3">
         <v>52900</v>
@@ -1656,8 +1656,8 @@
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
-        <v>16300</v>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F44" s="3">
         <v>22300</v>
@@ -1687,7 +1687,7 @@
         <v>862700</v>
       </c>
       <c r="E45" s="3">
-        <v>1000</v>
+        <v>468900</v>
       </c>
       <c r="F45" s="3">
         <v>2500</v>
@@ -1717,7 +1717,7 @@
         <v>866700</v>
       </c>
       <c r="E46" s="3">
-        <v>62400</v>
+        <v>470600</v>
       </c>
       <c r="F46" s="3">
         <v>90800</v>
@@ -1746,8 +1746,8 @@
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>3200</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>3700</v>
@@ -1776,8 +1776,8 @@
       <c r="D48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="3">
-        <v>155800</v>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F48" s="3">
         <v>181400</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>246200</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>256300</v>
@@ -1897,7 +1897,7 @@
         <v>3</v>
       </c>
       <c r="E52" s="3">
-        <v>3100</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>4300</v>
@@ -2014,8 +2014,8 @@
       <c r="D57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E57" s="3">
-        <v>59800</v>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F57" s="3">
         <v>62000</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>363600</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>332100</v>
@@ -2075,7 +2075,7 @@
         <v>709100</v>
       </c>
       <c r="E59" s="3">
-        <v>23900</v>
+        <v>613200</v>
       </c>
       <c r="F59" s="3">
         <v>18400</v>
@@ -2105,7 +2105,7 @@
         <v>709200</v>
       </c>
       <c r="E60" s="3">
-        <v>573300</v>
+        <v>616300</v>
       </c>
       <c r="F60" s="3">
         <v>525100</v>
@@ -2164,8 +2164,8 @@
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>5500</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>6200</v>
@@ -2707,11 +2707,11 @@
       <c r="D83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E83" s="3">
-        <v>20000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>31400</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G83" s="3">
         <v>41200</v>
@@ -2931,11 +2931,11 @@
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-5300</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>-11800</v>
